--- a/Design/Excel/ET/Datas/Product/InitialLayoutConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/InitialLayoutConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>洗碗台</t>
+          <t>水池／洗碗台</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1896,6 +1896,36 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>垃圾桶</t>
+        </is>
+      </c>
+      <c r="H19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/InitialLayoutConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/InitialLayoutConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1183,6 +1183,11 @@
           <t>InitialItemDefinitionId</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1225,6 +1230,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1267,6 +1277,11 @@
           <t>InitialItemDefinitionId</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1309,6 +1324,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1351,6 +1371,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1393,6 +1418,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1435,6 +1465,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1477,6 +1512,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1519,6 +1559,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1561,6 +1606,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1603,6 +1653,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1645,6 +1700,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1687,6 +1747,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1729,6 +1794,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1771,6 +1841,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1813,6 +1888,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1855,6 +1935,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1897,6 +1982,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1926,6 +2016,246 @@
       </c>
       <c r="H19">
         <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>榨汁机</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>贴单台</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>橙子台</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>果汁壶台</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>杯台</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/InitialLayoutConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/InitialLayoutConfig.xlsx
@@ -1,669 +1,730 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" r:id="Rf55f3c0dc7b54835"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
-    <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </x:numFmts>
-  <x:fonts count="24">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="12"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF800080"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="34">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF92D050"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="9">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4" tint="0.49998"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color theme="4"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="50">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="50">
-    <x:cellStyle name="常规" xfId="0"/>
-    <x:cellStyle name="千位分隔" xfId="1"/>
-    <x:cellStyle name="货币" xfId="2"/>
-    <x:cellStyle name="百分比" xfId="3"/>
-    <x:cellStyle name="千位分隔[0]" xfId="4"/>
-    <x:cellStyle name="货币[0]" xfId="5"/>
-    <x:cellStyle name="超链接" xfId="6"/>
-    <x:cellStyle name="已访问的超链接" xfId="7"/>
-    <x:cellStyle name="注释" xfId="8"/>
-    <x:cellStyle name="警告文本" xfId="9"/>
-    <x:cellStyle name="标题" xfId="10"/>
-    <x:cellStyle name="解释性文本" xfId="11"/>
-    <x:cellStyle name="标题 1" xfId="12"/>
-    <x:cellStyle name="标题 2" xfId="13"/>
-    <x:cellStyle name="标题 3" xfId="14"/>
-    <x:cellStyle name="标题 4" xfId="15"/>
-    <x:cellStyle name="输入" xfId="16"/>
-    <x:cellStyle name="输出" xfId="17"/>
-    <x:cellStyle name="计算" xfId="18"/>
-    <x:cellStyle name="检查单元格" xfId="19"/>
-    <x:cellStyle name="链接单元格" xfId="20"/>
-    <x:cellStyle name="汇总" xfId="21"/>
-    <x:cellStyle name="好" xfId="22"/>
-    <x:cellStyle name="差" xfId="23"/>
-    <x:cellStyle name="适中" xfId="24"/>
-    <x:cellStyle name="强调文字颜色 1" xfId="25"/>
-    <x:cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
-    <x:cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
-    <x:cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <x:cellStyle name="强调文字颜色 2" xfId="29"/>
-    <x:cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
-    <x:cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
-    <x:cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
-    <x:cellStyle name="强调文字颜色 3" xfId="33"/>
-    <x:cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <x:cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
-    <x:cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
-    <x:cellStyle name="强调文字颜色 4" xfId="37"/>
-    <x:cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
-    <x:cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
-    <x:cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
-    <x:cellStyle name="强调文字颜色 5" xfId="41"/>
-    <x:cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
-    <x:cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
-    <x:cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
-    <x:cellStyle name="强调文字颜色 6" xfId="45"/>
-    <x:cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
-    <x:cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
-    <x:cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
-    <x:cellStyle name="常规 2" xfId="49"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="24">
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="34">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="常规 2" xfId="49"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -940,90 +1001,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I57"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+    <col width="21.125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.75" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="2" min="3" max="4"/>
+    <col width="15.125" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9.625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.75" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11.75" customWidth="1" style="2" min="8" max="9"/>
+    <col width="6.75" customWidth="1" style="2" min="10" max="10"/>
+    <col width="9" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">##var</t>
+          <t>##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">StationDefinitionId</t>
+          <t>StationDefinitionId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">X</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orientation</t>
+          <t>Orientation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">InitialItemDefinitionId</t>
+          <t>InitialItemDefinitionId</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuVariant</t>
+          <t>MenuVariant</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">##type</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1033,12 +1099,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1050,74 +1116,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">##</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">StationDefinitionId</t>
+          <t>StationDefinitionId</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">X</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orientation</t>
+          <t>Orientation</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">InitialItemDefinitionId</t>
+          <t>InitialItemDefinitionId</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuVariant</t>
+          <t>MenuVariant</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1127,12 +1188,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">备料台</t>
+          <t>备料台</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1142,29 +1203,24 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1174,12 +1230,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">碗台</t>
+          <t>碗台</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1189,29 +1245,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1221,12 +1272,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">食材台</t>
+          <t>食材台</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1236,29 +1287,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1268,12 +1314,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">交接台</t>
+          <t>交接台</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,29 +1329,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1315,12 +1356,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">切配台</t>
+          <t>切配台</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1330,29 +1371,24 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1362,12 +1398,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">灶台</t>
+          <t>灶台</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1377,29 +1413,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1409,12 +1440,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">第二碗台</t>
+          <t>第二碗台</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1424,29 +1455,24 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1456,12 +1482,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">烤箱</t>
+          <t>烤箱</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,29 +1497,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1503,12 +1524,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">面包台</t>
+          <t>面包台</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1518,29 +1539,24 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1550,12 +1566,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">盘台</t>
+          <t>盘台</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1565,29 +1581,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1597,12 +1608,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">餐桌1</t>
+          <t>餐桌1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1612,29 +1623,24 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1644,12 +1650,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">餐桌2</t>
+          <t>餐桌2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1659,29 +1665,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1691,12 +1692,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">水池／洗碗台</t>
+          <t>水池／洗碗台</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1706,29 +1707,24 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1738,12 +1734,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">脏餐具池</t>
+          <t>脏餐具池</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1753,29 +1749,24 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1785,12 +1776,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">干净餐具池</t>
+          <t>干净餐具池</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1800,21 +1791,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>16</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>9</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -1824,10 +1810,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">垃圾桶</t>
-        </is>
-      </c>
-      <c r="H19">
+          <t>垃圾桶</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
@@ -1837,29 +1823,24 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1869,12 +1850,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">榨汁机</t>
+          <t>榨汁机</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1884,29 +1865,24 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1916,12 +1892,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">贴单台</t>
+          <t>贴单台</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1931,29 +1907,24 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1963,12 +1934,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">橙子台</t>
+          <t>橙子台</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1978,29 +1949,24 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2010,12 +1976,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">果汁壶台</t>
+          <t>果汁壶台</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2025,29 +1991,24 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2057,12 +2018,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">杯台</t>
+          <t>杯台</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2072,7 +2033,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str"/>
       <c r="B25" t="n">
         <v>22</v>
       </c>
@@ -2090,8 +2050,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G25" t="str">
-        <v>生菜台</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>生菜台</t>
+        </is>
       </c>
       <c r="H25" t="n">
         <v>22</v>
@@ -2103,7 +2065,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str"/>
       <c r="B26" t="n">
         <v>23</v>
       </c>
@@ -2121,8 +2082,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G26" t="str">
-        <v>黄瓜台</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>黄瓜台</t>
+        </is>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -2134,7 +2097,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str"/>
       <c r="B27" t="n">
         <v>24</v>
       </c>
@@ -2152,8 +2114,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G27" t="str">
-        <v>芝士台</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>芝士台</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>26</v>
@@ -2165,7 +2129,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str"/>
       <c r="B28" t="n">
         <v>25</v>
       </c>
@@ -2183,8 +2146,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G28" t="str">
-        <v>煎台</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>煎台</t>
+        </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2196,7 +2161,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str"/>
       <c r="B29" t="n">
         <v>26</v>
       </c>
@@ -2214,8 +2178,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G29" t="str">
-        <v>牛肉饼台</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>牛肉饼台</t>
+        </is>
       </c>
       <c r="H29" t="n">
         <v>33</v>
@@ -2227,7 +2193,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str"/>
       <c r="B30" t="n">
         <v>27</v>
       </c>
@@ -2245,8 +2210,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G30" t="str">
-        <v>搅拌机</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>搅拌机</t>
+        </is>
       </c>
       <c r="H30" t="n">
         <v>45</v>
@@ -2258,7 +2225,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str"/>
       <c r="B31" t="n">
         <v>28</v>
       </c>
@@ -2276,8 +2242,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G31" t="str">
-        <v>模具台</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>模具台</t>
+        </is>
       </c>
       <c r="H31" t="n">
         <v>47</v>
@@ -2289,7 +2257,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str"/>
       <c r="B32" t="n">
         <v>29</v>
       </c>
@@ -2307,8 +2274,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G32" t="str">
-        <v>甜品盘台</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>甜品盘台</t>
+        </is>
       </c>
       <c r="H32" t="n">
         <v>49</v>
@@ -2320,7 +2289,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str"/>
       <c r="B33" t="n">
         <v>30</v>
       </c>
@@ -2338,8 +2306,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G33" t="str">
-        <v>第二模具台</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>第二模具台</t>
+        </is>
       </c>
       <c r="H33" t="n">
         <v>47</v>
@@ -2351,7 +2321,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str"/>
       <c r="B34" t="n">
         <v>31</v>
       </c>
@@ -2369,8 +2338,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G34" t="str">
-        <v>磨豆机</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>磨豆机</t>
+        </is>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2382,7 +2353,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str"/>
       <c r="B35" t="n">
         <v>32</v>
       </c>
@@ -2400,8 +2370,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G35" t="str">
-        <v>咖啡机</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>咖啡机</t>
+        </is>
       </c>
       <c r="H35" t="n">
         <v>54</v>
@@ -2413,7 +2385,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str"/>
       <c r="B36" t="n">
         <v>33</v>
       </c>
@@ -2431,8 +2402,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G36" t="str">
-        <v>蒸汽机</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>蒸汽机</t>
+        </is>
       </c>
       <c r="H36" t="n">
         <v>55</v>
@@ -2444,7 +2417,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str"/>
       <c r="B37" t="n">
         <v>34</v>
       </c>
@@ -2462,8 +2434,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G37" t="str">
-        <v>热饮杯台</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>热饮杯台</t>
+        </is>
       </c>
       <c r="H37" t="n">
         <v>59</v>
@@ -2475,7 +2449,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str"/>
       <c r="B38" t="n">
         <v>35</v>
       </c>
@@ -2493,8 +2466,10 @@
           <t>Unrotated</t>
         </is>
       </c>
-      <c r="G38" t="str">
-        <v>第二奶缸台</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>第二奶缸台</t>
+        </is>
       </c>
       <c r="H38" t="n">
         <v>55</v>
@@ -2502,6 +2477,614 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>Cafe</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>15</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>洋葱台</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>64</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>牛肉末台</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>66</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>饺子皮台</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>67</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>拌馅盆台</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>72</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>蒸食盘台</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>71</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" t="n">
+        <v>17</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>蒸锅</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="n">
+        <v>18</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>13</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>取水台热水档</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="n">
+        <v>19</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>泡茶桶</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>87</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="n">
+        <v>20</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>煮珍珠台</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="n">
+        <v>21</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>调饮台</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>85</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>冷饮杯台</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>84</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>热茶杯台</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>59</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>11</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>小料罐台</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>86</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>茶饮贴单台</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>红茶叶台</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>77</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>生珍珠台</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>79</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>牛奶台</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>44</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>糖浆台</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>81</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>冰块台</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>83</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Tea</t>
         </is>
       </c>
     </row>
